--- a/1-standard-day/output/routeplan.xlsx
+++ b/1-standard-day/output/routeplan.xlsx
@@ -5942,7 +5942,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">placed 1415 km away (Post Office Drive Up Box, Sherwood Forest, Maryvil)</t>
+          <t xml:space="preserve">placed 1415 km away ()</t>
         </is>
       </c>
     </row>

--- a/1-standard-day/output/routeplan.xlsx
+++ b/1-standard-day/output/routeplan.xlsx
@@ -5942,7 +5942,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">placed 1415 km away ()</t>
+          <t xml:space="preserve">placed 1415 km away (Sherwood Forest, Maryville 37802)</t>
         </is>
       </c>
     </row>
